--- a/medford_monitory_dlya_zhestkoy_endoskopii.xlsx
+++ b/medford_monitory_dlya_zhestkoy_endoskopii.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Мониторы для жесткой эндоскопии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов MGB — всего 7 позиций.</t>
+          <t>Мониторы для жесткой эндоскопии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов MGB.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_monitory_dlya_zhestkoy_endoskopii.xlsx
+++ b/medford_monitory_dlya_zhestkoy_endoskopii.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать мониторы для жесткой эндоскопии для клиники?</t>
+          <t>Чем медицинский монитор отличается от обычного?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель, Разрешение, пиксели, Активная зона (ГxВ), мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Медицинский монитор для эндоскопии соответствует стандартам электробезопасности, имеет защитное антибликовое стекло и корпус, устойчивый к санитарной обработке дезинфектантами. Он рассчитан на высокую яркость и контрастность в условиях операционной. Бытовые дисплеи этим требованиям не отвечают и не предназначены для применения в стерильной зоне.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какое разрешение выбрать — Full HD или 4K?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Разрешение монитора согласуют с видеосистемой стойки. Для Full HD-камеры (1920×1080) достаточно Full HD-монитора, для 4K-камеры нужен 4K-дисплей (3840×2160). Ставить 4K-монитор к Full HD-камере смысла нет — детализацию определяет камера. В каталоге есть HD, Full HD и 4K-модели EVORAY под разные системы.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какую диагональ монитора выбрать?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены MGB. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Диагональ подбирают под размер операционной и дистанцию обзора. Компактные 19-дюймовые мониторы (EVORAY E190) подходят для небольших кабинетов и как вспомогательный экран, 24–32 дюйма — для операционной, где нужен крупный детальный кадр. В каталоге диагонали от 19 до 32 дюймов.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Подойдёт ли монитор к нашей стойке?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>При замене монитора проверяют совпадение входных интерфейсов с видеопроцессором и камерой, а также тип крепления (VESA, кронштейн). Монитор должен принимать сигнал существующей системы без дополнительных преобразователей и встать в стойку без переделок. Совместимость уточняют до покупки.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Зачем монитору высокая яркость?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Высокая яркость (часто от 500–600 кд/м²) и контрастность обеспечивают читаемость изображения при ярком операционном освещении и позволяют различать мелкие анатомические структуры. В условиях операционной обычный уровень яркости бытового дисплея недостаточен, поэтому медицинские мониторы рассчитаны на повышенные значения.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,120 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Можно ли обрабатывать монитор дезинфектантами?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Да, медицинские мониторы для эндоскопии имеют корпус и защитное стекло, устойчивые к санитарной обработке. Это необходимо, поскольку монитор находится в зоне операционной и регулярно подвергается дезинфекции. Конкретный перечень допустимых средств уточняют в документации на модель.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>monitory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Какие бренды мониторов представлены?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>В каталоге мониторы EVORAY (19–32 дюйма, HD, Full HD и 4K), немецкие MGB (AMM 261WTD, AMM 215WTD) и российский монитор для визуализации в хирургии «Крыло» 24″/19″. Модели различаются диагональю, разрешением и исполнением. Подбор ведут под видеосистему стойки и размер операционной.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>monitory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение на монитор?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Да. Монитор для жёсткой эндоскопии — медицинское изделие, его применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель у поставщика и убедитесь в его актуальности для применения в хирургии.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>monitory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Мониторы для жесткой эндоскопии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов MGB.</t>
+          <t>Мониторы для жёсткой эндоскопии — специализированные медицинские дисплеи высокой чёткости для трансляции изображения с эндовидеокамер во время диагностических и операционных вмешательств. В каталоге представлены модели EVORAY (19–32 дюйма, HD, Full HD и 4K), MGB (Германия) и российский монитор «Крыло» 24″/19″. Разрешение достигает 3840×2160 (4K) у моделей EVORAY S2785P и S3281P. Корпус рассчитан на условия операционной: соответствие медицинским стандартам электробезопасности и устойчивость к санитарной обработке. Диагонали от 19 до 32 дюймов подбирают под размер операционной.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Мониторы EVORAY в каталоге: характеристики по моделям</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое мониторы для жесткой эндоскопии</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3332,21 +3446,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Мониторы EVORAY в каталоге: характеристики по моделям</t>
         </is>
       </c>
     </row>
@@ -3358,209 +3470,111 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Диагональ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
+          <t>Разрешение</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Разрешение, пиксели</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Активная зона (ГxВ), мм</t>
+          <t>Класс</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Монитор 27” 4K эндоскопический-хирургический EVORAY S2785P</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>EVORAY E190</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>19"</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1280x1024</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>3840х2160</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>596.16х335.34</t>
+          <t>HD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ЖК-монитор с цифровым управлением MGB AMM 261WTD</t>
+          <t>EVORAY S2785P</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MGB</t>
+          <t>27"</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Германия</t>
+          <t>3840x2160</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>67332</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>4K</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Монитор 19” HD эндоскопический-хирургический EVORAY E190</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>EVORAY S3221P</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>32"</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Full HD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>1280x1024</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>376.32х301.06</t>
+          <t>Full HD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ЖК-монитор с цифровым управлением MGB AMM 215WTD</t>
+          <t>EVORAY S3281P</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MGB</t>
+          <t>32"</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Германия</t>
+          <t>3840x2160</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>67332</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Монитор 32" 4K эндоскопический-хирургический EVORAY S3281P</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Монитор для визуализации в хирургии Крыло 24″/19″</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>4K</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3572,7 +3586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3898,12 +3912,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите разрешение видеосистемы</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается мониторы для жесткой эндоскопии: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Монитор подбирают под камеру и видеопроцессор стойки. Если система Full HD, монитор Full HD (EVORAY S3221P, 32″) раскроет её полностью; для 4K-камеры нужен 4K-монитор (EVORAY S2785P 27″ или S3281P 32″, 3840×2160). Разрешение монитора согласуют с источником изображения.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3943,12 +3957,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите диагональ под операционную</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Диагонали в каталоге — от 19 до 32 дюймов. Компактный EVORAY E190 (19″) подходит для небольших кабинетов и вспомогательного экрана, 24–32 дюйма — для операционной, где хирургу нужен крупный детальный кадр. Диагональ выбирают исходя из размера помещения и дистанции обзора.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3988,12 +4002,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте яркость и контрастность</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель, Разрешение, пиксели, Активная зона (ГxВ), мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Для работы в условиях операционной важны высокая яркость (часто от 500–600 кд/м²) и контрастность. Они обеспечивают читаемость мелких анатомических структур при ярком операционном освещении. Параметры уточняют по характеристикам конкретной модели монитора.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4033,12 +4047,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Убедитесь в медицинском исполнении</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: MGB.</t>
+          <t>Медицинский монитор соответствует стандартам электробезопасности, имеет защитное антибликовое стекло и корпус, устойчивый к санитарной обработке. Это отличает его от бытовых дисплеев. Устойчивость к дезинфекции критична, поскольку монитор находится в зоне обработки операционной.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4078,12 +4092,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Сверьте входные интерфейсы</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>При замене монитора в готовую стойку проверьте совпадение входных интерфейсов с видеопроцессором и камерой. Монитор должен принимать сигнал существующей системы без дополнительных преобразователей. Заранее сверяют и крепления (VESA, кронштейн), чтобы дисплей встал в стойку без переделок.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4123,12 +4137,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте документы и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Убедитесь в наличии действующего регистрационного удостоверения Росздравнадзора на монитор как медицинское изделие. Уточните доступность сервиса и запчастей для выбранной модели, а также условия гарантийного обслуживания у поставщика до закупки.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4178,7 +4192,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Мониторы для жесткой эндоскопии подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены MGB. При выборе обращают внимание на страна производства, производитель, разрешение, активная зона (гxв), а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Монитор для жёсткой эндоскопии подбирают под видеосистему стойки: нет смысла ставить 4K-дисплей к Full HD-камере и наоборот. Смотрю на разрешение, диагональ под размер операционной и на то, что это именно медицинский монитор — с нужной яркостью, антибликовым стеклом и стойкостью корпуса к дезинфекции. При замене в готовую стойку главное — совпадение входных интерфейсов и креплений, чтобы монитор встал без переделок.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4462,13 +4476,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое мониторы для жесткой эндоскопии</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Мониторы для жесткой эндоскопии — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов MGB. Подберём вариант под задачи вашего отделения.</t>
+          <t>Монитор для жёсткой эндоскопии — специализированный медицинский дисплей для трансляции изображения с эндовидеокамеры во время диагностики и операций. Ключевые параметры — разрешение (от Full HD 1920×1080 до 4K 3840×2160), диагональ (19–32 дюйма), яркость и контрастность для условий операционной, а также медицинская электробезопасность и устойчивость корпуса к дезинфекции. В каталоге модели EVORAY (HD, Full HD, 4K), MGB (Германия) и российский монитор «Крыло». Разрешение и диагональ подбирают под видеосистему стойки и размер операционной.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4505,13 +4519,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Назначение монитора для жёсткой эндоскопии</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель, Разрешение, пиксели, Активная зона (ГxВ), мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Монитор для жёсткой эндоскопии — специализированный медицинский дисплей высокой чёткости для трансляции изображения с эндовидеокамер во время диагностических и операционных вмешательств. Он выводит картинку операционного поля в реальном времени, обеспечивая хирургу детальный обзор. От качества изображения зависит точность манипуляций, поэтому к таким мониторам предъявляют повышенные требования по разрешению, яркости и цветопередаче.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4548,13 +4562,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Разрешение и диагональ</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Разрешение мониторов варьирует от Full HD (1920×1080) до сверхвысокого 4K (3840×2160) для детализации мелких анатомических структур. Диагонали — от 19 до 32 дюймов и более, в зависимости от размера операционной и потребностей хирурга. В каталоге 4K-модели EVORAY S2785P (27″) и S3281P (32″), Full HD EVORAY S3221P (32″) и компактный HD-монитор E190 (19″).</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4591,13 +4605,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Требования операционной</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Мониторы для эндоскопии соответствуют медицинским стандартам электробезопасности, оснащаются защитным антибликовым стеклом и корпусом, устойчивым к санитарной обработке. Высокая яркость (часто от 500–600 кд/м²) и контрастность обеспечивают читаемость изображения при ярком операционном освещении. Эти характеристики отличают медицинский монитор от бытового дисплея и делают его пригодным для стерильной зоны.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4614,6 +4628,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Подбор и совместимость</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Монитор подбирают под видеосистему стойки: разрешение дисплея согласуют с камерой и видеопроцессором, диагональ — с размером операционной. При замене в готовую стойку проверяют совпадение входных интерфейсов и типа крепления, чтобы монитор встал без переделок. В каталоге модели EVORAY, немецкие MGB и российский монитор «Крыло» под разные конфигурации и бюджеты.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>monitory_dlya_zhestkoy_endoskopii</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
